--- a/themes/creditCards.xlsx
+++ b/themes/creditCards.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -510,261 +510,61 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Оформить заявку на кредитную карту «120 дней на максимум» можно по [ссылке]({{$temp.CC120DaysLink}})</t>
+          <t xml:space="preserve">      Для кредитной карты «Карта с кэшбеком» размер процентной ставки определяется банком индивидуально в диапазоне {{$temp.tariff.RateRange}} . Узнать точную ставку возможно после подачи заявки.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Оформить заявку на кредитную карту «120 дней на максимум» можно по [ссылке]({{$temp.CC120DaysLink}}).</t>
+          <t xml:space="preserve">      Для кредитной карты «Карта с кэшбеком» размер процентной ставки определяется банком индивидуально в диапазоне {{$temp.tariff.RateRange}}. Узнать точную ставку возможно после подачи заявки.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>убран лишний пробел перед точкой</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Также отправляю вам ссылку на подробный [тарифный план](https://uralsib.ru/api/directory-engine/files/rates/120dney_010626_biit7jme.pdf)</t>
+          <t xml:space="preserve">      На главной странице в разделе "Кредитная карта" будет отображаться информация о сумме и дате платежа, а также общая сумма долга.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Также отправляю вам ссылку на подробный [тарифный план](https://uralsib.ru/api/directory-engine/files/rates/120dney_010626_biit7jme.pdf).</t>
+          <t xml:space="preserve">      На главной странице в разделе «Кредитная карта» будет отображаться информация о сумме и дате платежа, а также общая сумма долга.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>прямые кавычки заменены на «ёлочки» — для единообразия с остальной базой</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>66</v>
+        <v>143</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Для кредитной карты «Карта с кэшбеком» размер процентной ставки определяется банком индивидуально в диапазоне {{$temp.tariff.RateRange}} . Узнать точную ставку возможно после подачи заявки.</t>
+          <t xml:space="preserve">      Деньги за покупки, сделанные по карте «120 дней на максимум» в первые 3 месяца после начала льготного периода нужно вернуть в конце 4 месяца. Первого числа, четвертого месяца льготный период обнуляется и начнется с первой покупки до 120 дней. </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Для кредитной карты «Карта с кэшбеком» размер процентной ставки определяется банком индивидуально в диапазоне {{$temp.tariff.RateRange}}. Узнать точную ставку возможно после подачи заявки.</t>
+          <t xml:space="preserve">      Деньги за покупки, сделанные по карте «120 дней на максимум» в первые 3 месяца после начала льготного периода, нужно вернуть в конце 4 месяца. Первого числа четвертого месяца льготный период обнуляется и начнется с первой покупки до 120 дней. </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>убран лишний пробел перед точкой</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>76</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Оформить заявку на кредитную карту «Карта с кэшбеком» можно по [ссылке]({{$temp.CCCashbackLink}})</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Оформить заявку на кредитную карту «Карта с кэшбеком» можно по [ссылке]({{$temp.CCCashbackLink}}).</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>77</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Также отправляю вам ссылку на подробный [тарифный план](https://uralsib.ru/api/directory-engine/files/rates/credcard_010626_tekfys6v.pdf)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Также отправляю вам ссылку на подробный [тарифный план](https://uralsib.ru/api/directory-engine/files/rates/credcard_010626_tekfys6v.pdf).</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>79</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    - Ознакомиться с полным списком кредитных карт и условиями их оформления, а также оставить заявку на получение карты вы сможете по [ссылке]({{$temp.CreditCardLink}})</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    - Ознакомиться с полным списком кредитных карт и условиями их оформления, а также оставить заявку на получение карты вы сможете по [ссылке]({{$temp.CreditCardLink}}).</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>89</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      На главной странице в разделе "Кредитная карта" будет отображаться информация о сумме и дате платежа, а также общая сумма долга.</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      На главной странице в разделе «Кредитная карта» будет отображаться информация о сумме и дате платежа, а также общая сумма долга.</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>прямые кавычки заменены на «ёлочки» — для единообразия с остальной базой</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>143</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Деньги за покупки, сделанные по карте «120 дней на максимум» в первые 3 месяца после начала льготного периода нужно вернуть в конце 4 месяца. Первого числа, четвертого месяца льготный период обнуляется и начнется с первой покупки до 120 дней. </t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Деньги за покупки, сделанные по карте «120 дней на максимум» в первые 3 месяца после начала льготного периода, нужно вернуть в конце 4 месяца. Первого числа четвертого месяца льготный период обнуляется и начнется с первой покупки до 120 дней. </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
           <t>убрана лишняя запятая («числа, четвертого» → «числа четвертого»); добавлена запятая, закрывающая причастный оборот, перед «нужно вернуть»</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>144</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Подробнее о льготном периоде можно прочитать на [сайте](https://uralsib.ru/kreditnye-karty/120-dney)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Подробнее о льготном периоде можно прочитать на [сайте](https://uralsib.ru/kreditnye-karty/120-dney).</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>155</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Подробнее о льготном периоде можно прочитать на [сайте](https://uralsib.ru/kreditnye-karty/120-dney)  </t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Подробнее о льготном периоде можно прочитать на [сайте](https://uralsib.ru/kreditnye-karty/120-dney).  </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>179</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Для оформления заявки в интернет-банке перейдите по [ссылке]({{ $temp.OpenCreditCardLink }})</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Для оформления заявки в интернет-банке перейдите по [ссылке]({{ $temp.OpenCreditCardLink }}).</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>181</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Agree: Для оформления заявки на кредитную карту с условиями из персонального предложения перейдите по [ссылке]({{ $temp.OpenOfferCardLink }})</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Agree: Для оформления заявки на кредитную карту с условиями из персонального предложения перейдите по [ссылке]({{ $temp.OpenOfferCardLink }}).</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>188</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Для оформления заявки в интернет-банке перейдите по [ссылке]({{ $temp.OpenCreditCardLink }})</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Для оформления заявки в интернет-банке перейдите по [ссылке]({{ $temp.OpenCreditCardLink }}).</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
         </is>
       </c>
     </row>
